--- a/InputFiles/CDS/phs004225/Base counts for studies.xlsx
+++ b/InputFiles/CDS/phs004225/Base counts for studies.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sofia\CRDC_CLI\TestData QA Env\GC March release\phs004225\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\davids3\CRDC_CLI\GC_2026_Sof\Commons_Automation\InputFiles\CDS\phs004225\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AA24D63-34EA-4999-A53B-D0358646DD65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92930BC9-790C-41ED-A4E7-0F6906C7866A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="305" xr2:uid="{87DCB0AD-B4CD-43F3-838A-2A7E125781A3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="305" xr2:uid="{87DCB0AD-B4CD-43F3-838A-2A7E125781A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="49">
   <si>
     <t>Study</t>
   </si>
@@ -144,9 +144,6 @@
   </si>
   <si>
     <t>Head-and-neck squamous cell carcinoma patients with CT taken during pre-treatment, mid-treatment, and post-treatment</t>
-  </si>
-  <si>
-    <t>QIN-SARCOMA</t>
   </si>
   <si>
     <t>The Cancer Genome Atlas Low Grade Glioma Collection</t>
@@ -294,7 +291,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -333,7 +330,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -670,7 +666,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4166E9C9-5759-4B43-81A3-2F6EC70CB7A0}">
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.7265625" customWidth="1"/>
@@ -706,11 +702,11 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="I1" s="14" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="36" x14ac:dyDescent="0.35">
@@ -735,10 +731,10 @@
       <c r="G2" s="12">
         <v>3042</v>
       </c>
-      <c r="H2" s="15">
-        <v>0</v>
-      </c>
-      <c r="I2" s="15">
+      <c r="H2" s="14">
+        <v>0</v>
+      </c>
+      <c r="I2" s="14">
         <v>0</v>
       </c>
     </row>
@@ -750,7 +746,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>15</v>
@@ -764,10 +760,10 @@
       <c r="G3" s="13">
         <v>110</v>
       </c>
-      <c r="H3" s="15">
-        <v>0</v>
-      </c>
-      <c r="I3" s="15">
+      <c r="H3" s="14">
+        <v>0</v>
+      </c>
+      <c r="I3" s="14">
         <v>0</v>
       </c>
     </row>
@@ -793,10 +789,10 @@
       <c r="G4" s="10">
         <v>7629</v>
       </c>
-      <c r="H4" s="15">
-        <v>0</v>
-      </c>
-      <c r="I4" s="15">
+      <c r="H4" s="14">
+        <v>0</v>
+      </c>
+      <c r="I4" s="14">
         <v>0</v>
       </c>
     </row>
@@ -808,7 +804,7 @@
         <v>8</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>10</v>
@@ -822,10 +818,10 @@
       <c r="G5" s="12">
         <v>4728</v>
       </c>
-      <c r="H5" s="15">
-        <v>0</v>
-      </c>
-      <c r="I5" s="15">
+      <c r="H5" s="14">
+        <v>0</v>
+      </c>
+      <c r="I5" s="14">
         <v>0</v>
       </c>
     </row>
@@ -851,10 +847,10 @@
       <c r="G6" s="10">
         <v>3358</v>
       </c>
-      <c r="H6" s="15">
-        <v>0</v>
-      </c>
-      <c r="I6" s="15">
+      <c r="H6" s="14">
+        <v>0</v>
+      </c>
+      <c r="I6" s="14">
         <v>0</v>
       </c>
     </row>
@@ -880,10 +876,10 @@
       <c r="G7" s="12">
         <v>1814</v>
       </c>
-      <c r="H7" s="15">
-        <v>0</v>
-      </c>
-      <c r="I7" s="15">
+      <c r="H7" s="14">
+        <v>0</v>
+      </c>
+      <c r="I7" s="14">
         <v>0</v>
       </c>
     </row>
@@ -909,10 +905,10 @@
       <c r="G8" s="11">
         <v>228</v>
       </c>
-      <c r="H8" s="15">
-        <v>0</v>
-      </c>
-      <c r="I8" s="15">
+      <c r="H8" s="14">
+        <v>0</v>
+      </c>
+      <c r="I8" s="14">
         <v>0</v>
       </c>
     </row>
@@ -938,10 +934,10 @@
       <c r="G9" s="11">
         <v>383</v>
       </c>
-      <c r="H9" s="15">
-        <v>0</v>
-      </c>
-      <c r="I9" s="15">
+      <c r="H9" s="14">
+        <v>0</v>
+      </c>
+      <c r="I9" s="14">
         <v>0</v>
       </c>
     </row>
@@ -953,7 +949,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>15</v>
@@ -967,10 +963,10 @@
       <c r="G10" s="12">
         <v>4956</v>
       </c>
-      <c r="H10" s="15">
-        <v>0</v>
-      </c>
-      <c r="I10" s="15">
+      <c r="H10" s="14">
+        <v>0</v>
+      </c>
+      <c r="I10" s="14">
         <v>0</v>
       </c>
     </row>
@@ -996,10 +992,10 @@
       <c r="G11" s="12">
         <v>6683</v>
       </c>
-      <c r="H11" s="15">
-        <v>0</v>
-      </c>
-      <c r="I11" s="15">
+      <c r="H11" s="14">
+        <v>0</v>
+      </c>
+      <c r="I11" s="14">
         <v>0</v>
       </c>
     </row>
@@ -1025,10 +1021,10 @@
       <c r="G12" s="11">
         <v>844</v>
       </c>
-      <c r="H12" s="15">
-        <v>0</v>
-      </c>
-      <c r="I12" s="15">
+      <c r="H12" s="14">
+        <v>0</v>
+      </c>
+      <c r="I12" s="14">
         <v>0</v>
       </c>
     </row>
@@ -1054,10 +1050,10 @@
       <c r="G13" s="10">
         <v>8307</v>
       </c>
-      <c r="H13" s="15">
-        <v>0</v>
-      </c>
-      <c r="I13" s="15">
+      <c r="H13" s="14">
+        <v>0</v>
+      </c>
+      <c r="I13" s="14">
         <v>0</v>
       </c>
     </row>
@@ -1083,10 +1079,10 @@
       <c r="G14" s="11">
         <v>349</v>
       </c>
-      <c r="H14" s="15">
-        <v>0</v>
-      </c>
-      <c r="I14" s="15">
+      <c r="H14" s="14">
+        <v>0</v>
+      </c>
+      <c r="I14" s="14">
         <v>0</v>
       </c>
     </row>
@@ -1098,7 +1094,7 @@
         <v>8</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>15</v>
@@ -1112,10 +1108,10 @@
       <c r="G15" s="10">
         <v>1915</v>
       </c>
-      <c r="H15" s="15">
-        <v>0</v>
-      </c>
-      <c r="I15" s="15">
+      <c r="H15" s="14">
+        <v>0</v>
+      </c>
+      <c r="I15" s="14">
         <v>0</v>
       </c>
     </row>
@@ -1141,10 +1137,10 @@
       <c r="G16" s="11">
         <v>371</v>
       </c>
-      <c r="H16" s="15">
-        <v>0</v>
-      </c>
-      <c r="I16" s="15">
+      <c r="H16" s="14">
+        <v>0</v>
+      </c>
+      <c r="I16" s="14">
         <v>0</v>
       </c>
     </row>
@@ -1170,10 +1166,10 @@
       <c r="G17" s="12">
         <v>1682</v>
       </c>
-      <c r="H17" s="15">
-        <v>0</v>
-      </c>
-      <c r="I17" s="15">
+      <c r="H17" s="14">
+        <v>0</v>
+      </c>
+      <c r="I17" s="14">
         <v>0</v>
       </c>
     </row>
@@ -1185,7 +1181,7 @@
         <v>8</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>15</v>
@@ -1199,10 +1195,10 @@
       <c r="G18" s="12">
         <v>2661</v>
       </c>
-      <c r="H18" s="15">
-        <v>0</v>
-      </c>
-      <c r="I18" s="15">
+      <c r="H18" s="14">
+        <v>0</v>
+      </c>
+      <c r="I18" s="14">
         <v>0</v>
       </c>
     </row>
@@ -1228,10 +1224,10 @@
       <c r="G19" s="13">
         <v>486</v>
       </c>
-      <c r="H19" s="15">
-        <v>0</v>
-      </c>
-      <c r="I19" s="15">
+      <c r="H19" s="14">
+        <v>0</v>
+      </c>
+      <c r="I19" s="14">
         <v>0</v>
       </c>
     </row>
@@ -1257,10 +1253,10 @@
       <c r="G20" s="12">
         <v>4036</v>
       </c>
-      <c r="H20" s="15">
-        <v>0</v>
-      </c>
-      <c r="I20" s="15">
+      <c r="H20" s="14">
+        <v>0</v>
+      </c>
+      <c r="I20" s="14">
         <v>0</v>
       </c>
     </row>
@@ -1286,10 +1282,10 @@
       <c r="G21" s="12">
         <v>5223</v>
       </c>
-      <c r="H21" s="15">
-        <v>0</v>
-      </c>
-      <c r="I21" s="15">
+      <c r="H21" s="14">
+        <v>0</v>
+      </c>
+      <c r="I21" s="14">
         <v>0</v>
       </c>
     </row>
@@ -1315,10 +1311,10 @@
       <c r="G22" s="13">
         <v>478</v>
       </c>
-      <c r="H22" s="15">
-        <v>0</v>
-      </c>
-      <c r="I22" s="15">
+      <c r="H22" s="14">
+        <v>0</v>
+      </c>
+      <c r="I22" s="14">
         <v>0</v>
       </c>
     </row>
@@ -1344,10 +1340,10 @@
       <c r="G23" s="13">
         <v>347</v>
       </c>
-      <c r="H23" s="15">
-        <v>0</v>
-      </c>
-      <c r="I23" s="15">
+      <c r="H23" s="14">
+        <v>0</v>
+      </c>
+      <c r="I23" s="14">
         <v>0</v>
       </c>
     </row>
@@ -1373,10 +1369,10 @@
       <c r="G24" s="13">
         <v>135</v>
       </c>
-      <c r="H24" s="15">
-        <v>0</v>
-      </c>
-      <c r="I24" s="15">
+      <c r="H24" s="14">
+        <v>0</v>
+      </c>
+      <c r="I24" s="14">
         <v>0</v>
       </c>
     </row>
@@ -1402,10 +1398,10 @@
       <c r="G25" s="10">
         <v>1942</v>
       </c>
-      <c r="H25" s="15">
-        <v>0</v>
-      </c>
-      <c r="I25" s="15">
+      <c r="H25" s="14">
+        <v>0</v>
+      </c>
+      <c r="I25" s="14">
         <v>0</v>
       </c>
     </row>
@@ -1431,126 +1427,126 @@
       <c r="G26" s="10">
         <v>3837</v>
       </c>
-      <c r="H26" s="15">
-        <v>0</v>
-      </c>
-      <c r="I26" s="15">
+      <c r="H26" s="14">
+        <v>0</v>
+      </c>
+      <c r="I26" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A27" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D27" s="3" t="s">
+      <c r="A27" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="4">
+      <c r="E27" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="8">
+        <v>130</v>
+      </c>
+      <c r="G27" s="12">
+        <v>1483</v>
+      </c>
+      <c r="H27" s="14">
+        <v>0</v>
+      </c>
+      <c r="I27" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="5">
+        <v>19</v>
+      </c>
+      <c r="G28" s="10">
+        <v>368</v>
+      </c>
+      <c r="H28" s="14">
+        <v>0</v>
+      </c>
+      <c r="I28" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="72" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G27" s="10">
-        <v>2168</v>
-      </c>
-      <c r="H27" s="15">
-        <v>0</v>
-      </c>
-      <c r="I27" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A28" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D28" s="7" t="s">
+      <c r="E29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="4">
+        <v>96</v>
+      </c>
+      <c r="G29" s="13">
+        <v>674</v>
+      </c>
+      <c r="H29" s="14">
+        <v>0</v>
+      </c>
+      <c r="I29" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="36" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E28" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="8">
-        <v>130</v>
-      </c>
-      <c r="G28" s="12">
-        <v>1483</v>
-      </c>
-      <c r="H28" s="15">
-        <v>0</v>
-      </c>
-      <c r="I28" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A29" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="5">
-        <v>19</v>
-      </c>
-      <c r="G29" s="10">
-        <v>368</v>
-      </c>
-      <c r="H29" s="15">
-        <v>0</v>
-      </c>
-      <c r="I29" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="72" x14ac:dyDescent="0.35">
-      <c r="A30" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="E30" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F30" s="4">
-        <v>96</v>
-      </c>
-      <c r="G30" s="13">
-        <v>674</v>
-      </c>
-      <c r="H30" s="15">
-        <v>0</v>
-      </c>
-      <c r="I30" s="15">
+        <v>262</v>
+      </c>
+      <c r="G30" s="10">
+        <v>5256</v>
+      </c>
+      <c r="H30" s="14">
+        <v>0</v>
+      </c>
+      <c r="I30" s="14">
         <v>0</v>
       </c>
     </row>
@@ -1562,57 +1558,57 @@
         <v>8</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="4">
+        <v>227</v>
+      </c>
+      <c r="G31" s="10">
+        <v>2561</v>
+      </c>
+      <c r="H31" s="14">
+        <v>0</v>
+      </c>
+      <c r="I31" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" s="4">
-        <v>262</v>
-      </c>
-      <c r="G31" s="10">
-        <v>5256</v>
-      </c>
-      <c r="H31" s="15">
-        <v>0</v>
-      </c>
-      <c r="I31" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="36" x14ac:dyDescent="0.35">
-      <c r="A32" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="4">
-        <v>227</v>
-      </c>
-      <c r="G32" s="10">
-        <v>2561</v>
-      </c>
-      <c r="H32" s="15">
-        <v>0</v>
-      </c>
-      <c r="I32" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E32" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="8">
+        <v>199</v>
+      </c>
+      <c r="G32" s="12">
+        <v>2275</v>
+      </c>
+      <c r="H32" s="14">
+        <v>0</v>
+      </c>
+      <c r="I32" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="48" x14ac:dyDescent="0.35">
       <c r="A33" s="6" t="s">
         <v>7</v>
       </c>
@@ -1620,7 +1616,7 @@
         <v>8</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>10</v>
@@ -1629,145 +1625,116 @@
         <v>11</v>
       </c>
       <c r="F33" s="8">
-        <v>199</v>
+        <v>70</v>
       </c>
       <c r="G33" s="12">
-        <v>2275</v>
-      </c>
-      <c r="H33" s="15">
-        <v>0</v>
-      </c>
-      <c r="I33" s="15">
+        <v>1835</v>
+      </c>
+      <c r="H33" s="14">
+        <v>0</v>
+      </c>
+      <c r="I33" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="48" x14ac:dyDescent="0.35">
-      <c r="A34" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D34" s="7" t="s">
+      <c r="A34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E34" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" s="8">
-        <v>70</v>
-      </c>
-      <c r="G34" s="12">
-        <v>1835</v>
-      </c>
-      <c r="H34" s="15">
-        <v>0</v>
-      </c>
-      <c r="I34" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="48" x14ac:dyDescent="0.35">
-      <c r="A35" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C35" s="3" t="s">
+      <c r="E34" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="4">
+        <v>156</v>
+      </c>
+      <c r="G34" s="10">
+        <v>3127</v>
+      </c>
+      <c r="H34" s="14">
+        <v>0</v>
+      </c>
+      <c r="I34" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="36" x14ac:dyDescent="0.35">
+      <c r="A35" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="8">
+        <v>46</v>
+      </c>
+      <c r="G35" s="11">
+        <v>92</v>
+      </c>
+      <c r="H35" s="14">
+        <v>0</v>
+      </c>
+      <c r="I35" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="72" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="4">
         <v>40</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35" s="4">
-        <v>156</v>
-      </c>
-      <c r="G35" s="10">
-        <v>3127</v>
-      </c>
-      <c r="H35" s="15">
-        <v>0</v>
-      </c>
-      <c r="I35" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="36" x14ac:dyDescent="0.35">
-      <c r="A36" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F36" s="8">
-        <v>46</v>
-      </c>
-      <c r="G36" s="11">
-        <v>92</v>
-      </c>
-      <c r="H36" s="15">
-        <v>0</v>
-      </c>
-      <c r="I36" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="72" x14ac:dyDescent="0.35">
-      <c r="A37" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" s="4">
-        <v>40</v>
-      </c>
-      <c r="G37" s="13">
+      <c r="G36" s="13">
         <v>600</v>
       </c>
-      <c r="H37" s="15">
-        <v>0</v>
-      </c>
-      <c r="I37" s="15">
-        <v>0</v>
-      </c>
+      <c r="H36" s="14">
+        <v>0</v>
+      </c>
+      <c r="I36" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="H39" s="15"/>
-      <c r="I39" s="15"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I37">
-    <sortCondition ref="C1:C37"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I36">
+    <sortCondition ref="C1:C36"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="A25" r:id="rId1" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{26299254-E51A-40D0-85FE-6F4EB16635E5}"/>
@@ -1778,8 +1745,8 @@
     <hyperlink ref="B6" r:id="rId6" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{BD6E7187-EE48-4247-8A7C-9ABAC6506C96}"/>
     <hyperlink ref="A12" r:id="rId7" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{DD1514E7-87BB-453E-9793-EDD4C19E9361}"/>
     <hyperlink ref="B12" r:id="rId8" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{BBF85B81-38C4-4F53-8D81-B151CDD475CE}"/>
-    <hyperlink ref="A31" r:id="rId9" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{FE1BD8AD-5455-46B2-ACA6-2A5554C91AC6}"/>
-    <hyperlink ref="B31" r:id="rId10" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{A5ECDF9D-65E9-42E5-8D2B-0B47661979EF}"/>
+    <hyperlink ref="A30" r:id="rId9" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{FE1BD8AD-5455-46B2-ACA6-2A5554C91AC6}"/>
+    <hyperlink ref="B30" r:id="rId10" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{A5ECDF9D-65E9-42E5-8D2B-0B47661979EF}"/>
     <hyperlink ref="A20" r:id="rId11" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{7069A0C3-467A-44E2-9113-20D2763F1082}"/>
     <hyperlink ref="B20" r:id="rId12" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{C7962694-F1B2-4DEE-836B-E5912E56C3A2}"/>
     <hyperlink ref="A23" r:id="rId13" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{7F8F65FE-2F2F-4C91-A371-A98C0DB72191}"/>
@@ -1804,44 +1771,42 @@
     <hyperlink ref="B11" r:id="rId32" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{612894AC-3D1E-48AB-9F9C-B67790D26F6F}"/>
     <hyperlink ref="A4" r:id="rId33" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{26038193-E237-44F2-BD07-ECD38151AC29}"/>
     <hyperlink ref="B4" r:id="rId34" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{D1DA0BCD-9E58-421E-906C-637943505C92}"/>
-    <hyperlink ref="A36" r:id="rId35" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{4F0C6F24-5B59-4E6A-8327-CC3F2FB07AD8}"/>
-    <hyperlink ref="B36" r:id="rId36" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{C7DF2109-AE4C-405C-A57F-AE3BFB08B21C}"/>
-    <hyperlink ref="A37" r:id="rId37" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{6249A771-6525-40D4-9489-3B38129D60CC}"/>
-    <hyperlink ref="B37" r:id="rId38" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{2287282B-7718-409C-9E5A-55D0493D8A16}"/>
+    <hyperlink ref="A35" r:id="rId35" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{4F0C6F24-5B59-4E6A-8327-CC3F2FB07AD8}"/>
+    <hyperlink ref="B35" r:id="rId36" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{C7DF2109-AE4C-405C-A57F-AE3BFB08B21C}"/>
+    <hyperlink ref="A36" r:id="rId37" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{6249A771-6525-40D4-9489-3B38129D60CC}"/>
+    <hyperlink ref="B36" r:id="rId38" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{2287282B-7718-409C-9E5A-55D0493D8A16}"/>
     <hyperlink ref="A8" r:id="rId39" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{BFF34473-B330-420D-A235-EF2CEF855D44}"/>
     <hyperlink ref="B8" r:id="rId40" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{C01C60AF-6C75-4197-B881-A4AC5B815786}"/>
-    <hyperlink ref="A30" r:id="rId41" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{528AEB44-301C-4B61-BA4D-06E003DC2CF8}"/>
-    <hyperlink ref="B30" r:id="rId42" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{BF444C2E-39D2-4746-AED3-B77140872AA0}"/>
+    <hyperlink ref="A29" r:id="rId41" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{528AEB44-301C-4B61-BA4D-06E003DC2CF8}"/>
+    <hyperlink ref="B29" r:id="rId42" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{BF444C2E-39D2-4746-AED3-B77140872AA0}"/>
     <hyperlink ref="A2" r:id="rId43" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{CFF0005E-BDC8-48E4-8EBE-4D29F34A4A91}"/>
     <hyperlink ref="B2" r:id="rId44" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{4CED5A9D-2E2C-4EB4-9294-B9148324F795}"/>
     <hyperlink ref="A19" r:id="rId45" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{DDAAEF31-68DF-421D-9913-4C67A93A789A}"/>
     <hyperlink ref="B19" r:id="rId46" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{A3ABF6C6-66FC-41B6-A376-C36F0574D34A}"/>
     <hyperlink ref="A16" r:id="rId47" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{D951E34C-6DC3-4348-8F84-674D5F9F53CB}"/>
     <hyperlink ref="B16" r:id="rId48" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{278ECE19-5F63-4783-B660-A90B2F1696DE}"/>
-    <hyperlink ref="A27" r:id="rId49" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{C875606F-507E-4404-9D7B-BFE2F779FC06}"/>
-    <hyperlink ref="B27" r:id="rId50" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{A7196174-177F-45F3-9854-F2AD28C72F3F}"/>
-    <hyperlink ref="A33" r:id="rId51" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{0378A0CE-5978-46F1-98B2-50D8C77CA00D}"/>
-    <hyperlink ref="B33" r:id="rId52" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{D200AE98-9099-4DE5-812B-C7DE9325224B}"/>
-    <hyperlink ref="A32" r:id="rId53" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{250FEC17-424E-471B-913E-1FA5598C34DA}"/>
-    <hyperlink ref="B32" r:id="rId54" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{5AB1480E-DE11-4E36-B673-58D8ACA97B42}"/>
-    <hyperlink ref="A28" r:id="rId55" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{97BFA605-F0ED-4BA7-90EA-0B61593B24AF}"/>
-    <hyperlink ref="B28" r:id="rId56" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{71A43DAC-9C36-47DD-AC11-A730B95E8548}"/>
-    <hyperlink ref="A35" r:id="rId57" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{38516957-E8C4-4760-A05E-3F157D366C26}"/>
-    <hyperlink ref="B35" r:id="rId58" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{341D51B4-2324-41CB-A78B-4F59110C8FF0}"/>
-    <hyperlink ref="A34" r:id="rId59" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{51A7A01C-AA85-46A6-BF57-D4E23FDC4DFC}"/>
-    <hyperlink ref="B34" r:id="rId60" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{B054BDD1-CD9C-489C-8F93-E87DA59CEE48}"/>
-    <hyperlink ref="A29" r:id="rId61" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{CE8FED3E-7E3E-43A1-8FD2-2DA9CBC4272A}"/>
-    <hyperlink ref="B29" r:id="rId62" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{812729A0-8186-4240-A235-65DEB7DA46E9}"/>
-    <hyperlink ref="A18" r:id="rId63" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{39778C5E-5B3E-4E53-BCE5-9ADAF0859036}"/>
-    <hyperlink ref="B18" r:id="rId64" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{03FEBA7E-8829-4248-9805-31AEAF41FF8F}"/>
-    <hyperlink ref="A15" r:id="rId65" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{D11F8DB4-F08E-4EE8-9764-8E9BAED98F88}"/>
-    <hyperlink ref="B15" r:id="rId66" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{1D4DFAE6-ADCB-49D3-8D4D-6B9BBE42C49B}"/>
-    <hyperlink ref="A10" r:id="rId67" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{344C7A55-D58B-4956-AB58-E006037044FB}"/>
-    <hyperlink ref="B10" r:id="rId68" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{F5E98ECA-B3C5-4CBB-8CF6-3695A337371E}"/>
-    <hyperlink ref="A3" r:id="rId69" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{2CAB4DAB-EBC1-4405-8793-76DE5795F35D}"/>
-    <hyperlink ref="B3" r:id="rId70" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{9E66E34D-430E-4C90-BA35-78E61B1FD78A}"/>
-    <hyperlink ref="A5" r:id="rId71" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{C66AF21C-F1A1-4F6E-A026-78736ED7122F}"/>
-    <hyperlink ref="B5" r:id="rId72" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{2134F6FE-BB93-479A-A8C6-81BDB9034268}"/>
+    <hyperlink ref="A32" r:id="rId49" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{0378A0CE-5978-46F1-98B2-50D8C77CA00D}"/>
+    <hyperlink ref="B32" r:id="rId50" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{D200AE98-9099-4DE5-812B-C7DE9325224B}"/>
+    <hyperlink ref="A31" r:id="rId51" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{250FEC17-424E-471B-913E-1FA5598C34DA}"/>
+    <hyperlink ref="B31" r:id="rId52" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{5AB1480E-DE11-4E36-B673-58D8ACA97B42}"/>
+    <hyperlink ref="A27" r:id="rId53" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{97BFA605-F0ED-4BA7-90EA-0B61593B24AF}"/>
+    <hyperlink ref="B27" r:id="rId54" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{71A43DAC-9C36-47DD-AC11-A730B95E8548}"/>
+    <hyperlink ref="A34" r:id="rId55" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{38516957-E8C4-4760-A05E-3F157D366C26}"/>
+    <hyperlink ref="B34" r:id="rId56" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{341D51B4-2324-41CB-A78B-4F59110C8FF0}"/>
+    <hyperlink ref="A33" r:id="rId57" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{51A7A01C-AA85-46A6-BF57-D4E23FDC4DFC}"/>
+    <hyperlink ref="B33" r:id="rId58" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{B054BDD1-CD9C-489C-8F93-E87DA59CEE48}"/>
+    <hyperlink ref="A28" r:id="rId59" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{CE8FED3E-7E3E-43A1-8FD2-2DA9CBC4272A}"/>
+    <hyperlink ref="B28" r:id="rId60" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{812729A0-8186-4240-A235-65DEB7DA46E9}"/>
+    <hyperlink ref="A18" r:id="rId61" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{39778C5E-5B3E-4E53-BCE5-9ADAF0859036}"/>
+    <hyperlink ref="B18" r:id="rId62" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{03FEBA7E-8829-4248-9805-31AEAF41FF8F}"/>
+    <hyperlink ref="A15" r:id="rId63" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{D11F8DB4-F08E-4EE8-9764-8E9BAED98F88}"/>
+    <hyperlink ref="B15" r:id="rId64" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{1D4DFAE6-ADCB-49D3-8D4D-6B9BBE42C49B}"/>
+    <hyperlink ref="A10" r:id="rId65" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{344C7A55-D58B-4956-AB58-E006037044FB}"/>
+    <hyperlink ref="B10" r:id="rId66" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{F5E98ECA-B3C5-4CBB-8CF6-3695A337371E}"/>
+    <hyperlink ref="A3" r:id="rId67" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{2CAB4DAB-EBC1-4405-8793-76DE5795F35D}"/>
+    <hyperlink ref="B3" r:id="rId68" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{9E66E34D-430E-4C90-BA35-78E61B1FD78A}"/>
+    <hyperlink ref="A5" r:id="rId69" location="/study/phs004225" display="https://general-qa2.datacommons.cancer.gov/ - /study/phs004225" xr:uid="{C66AF21C-F1A1-4F6E-A026-78736ED7122F}"/>
+    <hyperlink ref="B5" r:id="rId70" location="/data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" display="https://general-qa2.datacommons.cancer.gov/ - /data/%7B%22phs_accession%22%3A%5B%22phs004225%22%5D%7D" xr:uid="{2134F6FE-BB93-479A-A8C6-81BDB9034268}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
